--- a/type_products.xlsx
+++ b/type_products.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8268aba086fcb9b8/KDA_Trinh Võ/KDA data/PYTHON_OPERATION/ma_shondo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="8_{D6F73DBA-9E9C-4B20-8B5F-A694861B8E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4DE217AA-DAC0-4DA4-8079-3A8546DBF26F}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="8_{D6F73DBA-9E9C-4B20-8B5F-A694861B8E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A7888DA-4A14-4DC5-BC70-CC92400D7CCA}"/>
   <bookViews>
-    <workbookView xWindow="2772" yWindow="1668" windowWidth="17280" windowHeight="8880" xr2:uid="{4FBC304B-1485-4E2B-9A5F-5219FF202583}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{4FBC304B-1485-4E2B-9A5F-5219FF202583}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="123">
   <si>
     <t>default_code</t>
   </si>
@@ -402,6 +402,12 @@
   </si>
   <si>
     <t>SN32222</t>
+  </si>
+  <si>
+    <t>F102020</t>
+  </si>
+  <si>
+    <t>GIM4040</t>
   </si>
 </sst>
 </file>
@@ -777,14 +783,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B6F4F5F-BD9B-439B-856A-4846BF0AF5A9}">
-  <dimension ref="A1:B118"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B120"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -792,7 +798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -800,7 +806,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -808,7 +814,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -816,7 +822,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -824,7 +830,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -832,7 +838,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -840,7 +846,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -848,7 +854,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -856,7 +862,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -864,7 +870,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -872,7 +878,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -880,7 +886,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -888,7 +894,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -896,7 +902,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -904,7 +910,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -912,7 +918,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -920,7 +926,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -928,7 +934,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -936,7 +942,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -944,7 +950,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -952,7 +958,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -960,7 +966,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -968,7 +974,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -976,7 +982,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -984,7 +990,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -992,7 +998,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -1000,7 +1006,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>28</v>
       </c>
@@ -1008,7 +1014,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>29</v>
       </c>
@@ -1016,7 +1022,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>30</v>
       </c>
@@ -1024,7 +1030,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>31</v>
       </c>
@@ -1032,7 +1038,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>32</v>
       </c>
@@ -1040,7 +1046,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>33</v>
       </c>
@@ -1048,7 +1054,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>34</v>
       </c>
@@ -1056,7 +1062,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>35</v>
       </c>
@@ -1064,7 +1070,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>36</v>
       </c>
@@ -1072,7 +1078,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>37</v>
       </c>
@@ -1080,7 +1086,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>38</v>
       </c>
@@ -1088,7 +1094,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>39</v>
       </c>
@@ -1096,7 +1102,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>40</v>
       </c>
@@ -1104,7 +1110,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>41</v>
       </c>
@@ -1112,7 +1118,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>42</v>
       </c>
@@ -1120,7 +1126,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>43</v>
       </c>
@@ -1128,7 +1134,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>44</v>
       </c>
@@ -1136,7 +1142,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>45</v>
       </c>
@@ -1144,7 +1150,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>46</v>
       </c>
@@ -1152,7 +1158,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>47</v>
       </c>
@@ -1160,7 +1166,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>48</v>
       </c>
@@ -1168,7 +1174,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>49</v>
       </c>
@@ -1176,7 +1182,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>50</v>
       </c>
@@ -1184,7 +1190,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>51</v>
       </c>
@@ -1192,7 +1198,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>52</v>
       </c>
@@ -1200,7 +1206,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>53</v>
       </c>
@@ -1208,7 +1214,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>54</v>
       </c>
@@ -1216,7 +1222,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>55</v>
       </c>
@@ -1224,7 +1230,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>56</v>
       </c>
@@ -1232,7 +1238,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>57</v>
       </c>
@@ -1240,7 +1246,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>58</v>
       </c>
@@ -1248,7 +1254,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>59</v>
       </c>
@@ -1256,7 +1262,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>60</v>
       </c>
@@ -1264,7 +1270,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>61</v>
       </c>
@@ -1272,7 +1278,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>65</v>
       </c>
@@ -1280,7 +1286,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>66</v>
       </c>
@@ -1288,7 +1294,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>67</v>
       </c>
@@ -1296,7 +1302,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>68</v>
       </c>
@@ -1304,7 +1310,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>69</v>
       </c>
@@ -1312,7 +1318,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>70</v>
       </c>
@@ -1320,7 +1326,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>71</v>
       </c>
@@ -1328,7 +1334,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>72</v>
       </c>
@@ -1336,7 +1342,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>73</v>
       </c>
@@ -1344,7 +1350,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>74</v>
       </c>
@@ -1352,7 +1358,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>75</v>
       </c>
@@ -1360,7 +1366,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>76</v>
       </c>
@@ -1368,7 +1374,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>77</v>
       </c>
@@ -1376,7 +1382,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>78</v>
       </c>
@@ -1384,7 +1390,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>79</v>
       </c>
@@ -1392,7 +1398,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>80</v>
       </c>
@@ -1400,7 +1406,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>81</v>
       </c>
@@ -1408,7 +1414,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>82</v>
       </c>
@@ -1416,7 +1422,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>83</v>
       </c>
@@ -1424,7 +1430,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>84</v>
       </c>
@@ -1432,7 +1438,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>85</v>
       </c>
@@ -1440,7 +1446,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>86</v>
       </c>
@@ -1448,7 +1454,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>87</v>
       </c>
@@ -1456,7 +1462,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>88</v>
       </c>
@@ -1464,7 +1470,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>89</v>
       </c>
@@ -1472,7 +1478,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>90</v>
       </c>
@@ -1480,7 +1486,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>91</v>
       </c>
@@ -1488,7 +1494,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>92</v>
       </c>
@@ -1496,7 +1502,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>93</v>
       </c>
@@ -1504,7 +1510,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>94</v>
       </c>
@@ -1512,7 +1518,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>95</v>
       </c>
@@ -1520,7 +1526,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>96</v>
       </c>
@@ -1528,7 +1534,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>97</v>
       </c>
@@ -1536,7 +1542,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>98</v>
       </c>
@@ -1544,7 +1550,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>62</v>
       </c>
@@ -1552,7 +1558,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>63</v>
       </c>
@@ -1560,7 +1566,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>64</v>
       </c>
@@ -1568,7 +1574,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>99</v>
       </c>
@@ -1576,7 +1582,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>100</v>
       </c>
@@ -1584,7 +1590,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>104</v>
       </c>
@@ -1592,7 +1598,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>105</v>
       </c>
@@ -1600,7 +1606,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>106</v>
       </c>
@@ -1608,7 +1614,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>107</v>
       </c>
@@ -1616,7 +1622,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>108</v>
       </c>
@@ -1624,7 +1630,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>109</v>
       </c>
@@ -1632,7 +1638,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>110</v>
       </c>
@@ -1640,7 +1646,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>111</v>
       </c>
@@ -1648,7 +1654,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>112</v>
       </c>
@@ -1656,7 +1662,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>103</v>
       </c>
@@ -1664,7 +1670,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>113</v>
       </c>
@@ -1672,7 +1678,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>114</v>
       </c>
@@ -1680,7 +1686,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>115</v>
       </c>
@@ -1688,7 +1694,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>116</v>
       </c>
@@ -1696,7 +1702,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>117</v>
       </c>
@@ -1704,7 +1710,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>118</v>
       </c>
@@ -1712,7 +1718,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>119</v>
       </c>
@@ -1720,11 +1726,27 @@
         <v>101</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>120</v>
       </c>
       <c r="B118" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
+        <v>121</v>
+      </c>
+      <c r="B119" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
+        <v>122</v>
+      </c>
+      <c r="B120" t="s">
         <v>101</v>
       </c>
     </row>

--- a/type_products.xlsx
+++ b/type_products.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8268aba086fcb9b8/KDA_Trinh Võ/KDA data/PYTHON_OPERATION/ma_shondo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="8_{D6F73DBA-9E9C-4B20-8B5F-A694861B8E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A7888DA-4A14-4DC5-BC70-CC92400D7CCA}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="8_{D6F73DBA-9E9C-4B20-8B5F-A694861B8E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3087FD7-E749-4E6A-87EB-3A9902F01808}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{4FBC304B-1485-4E2B-9A5F-5219FF202583}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$125</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="128">
   <si>
     <t>default_code</t>
   </si>
@@ -408,6 +411,21 @@
   </si>
   <si>
     <t>GIM4040</t>
+  </si>
+  <si>
+    <t>EZI2425</t>
+  </si>
+  <si>
+    <t>CH40009</t>
+  </si>
+  <si>
+    <t>CH47171</t>
+  </si>
+  <si>
+    <t>CH41010</t>
+  </si>
+  <si>
+    <t>CH43535</t>
   </si>
 </sst>
 </file>
@@ -783,7 +801,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B6F4F5F-BD9B-439B-856A-4846BF0AF5A9}">
-  <dimension ref="A1:B120"/>
+  <dimension ref="A1:B125"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
@@ -1750,6 +1768,46 @@
         <v>101</v>
       </c>
     </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A121" t="s">
+        <v>123</v>
+      </c>
+      <c r="B121" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>124</v>
+      </c>
+      <c r="B122" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
+        <v>125</v>
+      </c>
+      <c r="B123" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
+        <v>126</v>
+      </c>
+      <c r="B124" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>127</v>
+      </c>
+      <c r="B125" t="s">
+        <v>101</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>

--- a/type_products.xlsx
+++ b/type_products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8268aba086fcb9b8/KDA_Trinh Võ/KDA data/PYTHON_OPERATION/ma_shondo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="8_{D6F73DBA-9E9C-4B20-8B5F-A694861B8E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3087FD7-E749-4E6A-87EB-3A9902F01808}"/>
+  <xr:revisionPtr revIDLastSave="56" documentId="8_{D6F73DBA-9E9C-4B20-8B5F-A694861B8E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FD199AD-1F21-4748-B706-EAA4F8198B0C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{4FBC304B-1485-4E2B-9A5F-5219FF202583}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="129">
   <si>
     <t>default_code</t>
   </si>
@@ -426,6 +426,9 @@
   </si>
   <si>
     <t>CH43535</t>
+  </si>
+  <si>
+    <t>GIM0009</t>
   </si>
 </sst>
 </file>
@@ -801,7 +804,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B6F4F5F-BD9B-439B-856A-4846BF0AF5A9}">
-  <dimension ref="A1:B125"/>
+  <dimension ref="A1:B126"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
@@ -1808,6 +1811,14 @@
         <v>101</v>
       </c>
     </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
+        <v>128</v>
+      </c>
+      <c r="B126" t="s">
+        <v>101</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>

--- a/type_products.xlsx
+++ b/type_products.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8268aba086fcb9b8/KDA_Trinh Võ/KDA data/PYTHON_OPERATION/ma_shondo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="56" documentId="8_{D6F73DBA-9E9C-4B20-8B5F-A694861B8E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FD199AD-1F21-4748-B706-EAA4F8198B0C}"/>
+  <xr:revisionPtr revIDLastSave="65" documentId="8_{D6F73DBA-9E9C-4B20-8B5F-A694861B8E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C70605E-0A4B-40EF-B296-9AE7CD6355C7}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{4FBC304B-1485-4E2B-9A5F-5219FF202583}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4FBC304B-1485-4E2B-9A5F-5219FF202583}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="143">
   <si>
     <t>default_code</t>
   </si>
@@ -429,6 +429,48 @@
   </si>
   <si>
     <t>GIM0009</t>
+  </si>
+  <si>
+    <t>GIM5050</t>
+  </si>
+  <si>
+    <t>GIM2526</t>
+  </si>
+  <si>
+    <t>GIM3030</t>
+  </si>
+  <si>
+    <t>GIM0008</t>
+  </si>
+  <si>
+    <t>GIM7071</t>
+  </si>
+  <si>
+    <t>E4Z0009</t>
+  </si>
+  <si>
+    <t>E4Z1010</t>
+  </si>
+  <si>
+    <t>EZI2223</t>
+  </si>
+  <si>
+    <t>SUK0008</t>
+  </si>
+  <si>
+    <t>SUK0000</t>
+  </si>
+  <si>
+    <t>DRE0008</t>
+  </si>
+  <si>
+    <t>DRE1011</t>
+  </si>
+  <si>
+    <t>SUK7071</t>
+  </si>
+  <si>
+    <t>SUK0960</t>
   </si>
 </sst>
 </file>
@@ -804,7 +846,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B6F4F5F-BD9B-439B-856A-4846BF0AF5A9}">
-  <dimension ref="A1:B126"/>
+  <dimension ref="A1:B140"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
@@ -1819,6 +1861,118 @@
         <v>101</v>
       </c>
     </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
+        <v>129</v>
+      </c>
+      <c r="B127" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
+        <v>130</v>
+      </c>
+      <c r="B128" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A129" t="s">
+        <v>131</v>
+      </c>
+      <c r="B129" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A130" t="s">
+        <v>132</v>
+      </c>
+      <c r="B130" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A131" t="s">
+        <v>133</v>
+      </c>
+      <c r="B131" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A132" t="s">
+        <v>134</v>
+      </c>
+      <c r="B132" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A133" t="s">
+        <v>135</v>
+      </c>
+      <c r="B133" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A134" t="s">
+        <v>136</v>
+      </c>
+      <c r="B134" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A135" t="s">
+        <v>137</v>
+      </c>
+      <c r="B135" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A136" t="s">
+        <v>138</v>
+      </c>
+      <c r="B136" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A137" t="s">
+        <v>139</v>
+      </c>
+      <c r="B137" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A138" t="s">
+        <v>140</v>
+      </c>
+      <c r="B138" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A139" t="s">
+        <v>141</v>
+      </c>
+      <c r="B139" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
+        <v>142</v>
+      </c>
+      <c r="B140" t="s">
+        <v>101</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
